--- a/nr-init/ig/CodeSystem-cs-fr-FR-v3-Confidentiality.xlsx
+++ b/nr-init/ig/CodeSystem-cs-fr-FR-v3-Confidentiality.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T17:10:15+00:00</t>
+    <t>2025-12-22T17:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-init/ig/CodeSystem-cs-fr-FR-v3-Confidentiality.xlsx
+++ b/nr-init/ig/CodeSystem-cs-fr-FR-v3-Confidentiality.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T17:17:12+00:00</t>
+    <t>2025-12-22T17:21:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-init/ig/CodeSystem-cs-fr-FR-v3-Confidentiality.xlsx
+++ b/nr-init/ig/CodeSystem-cs-fr-FR-v3-Confidentiality.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T17:21:11+00:00</t>
+    <t>2025-12-22T17:32:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-init/ig/CodeSystem-cs-fr-FR-v3-Confidentiality.xlsx
+++ b/nr-init/ig/CodeSystem-cs-fr-FR-v3-Confidentiality.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T17:32:51+00:00</t>
+    <t>2025-12-22T17:37:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-init/ig/CodeSystem-cs-fr-FR-v3-Confidentiality.xlsx
+++ b/nr-init/ig/CodeSystem-cs-fr-FR-v3-Confidentiality.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T17:37:51+00:00</t>
+    <t>2025-12-22T17:43:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-init/ig/CodeSystem-cs-fr-FR-v3-Confidentiality.xlsx
+++ b/nr-init/ig/CodeSystem-cs-fr-FR-v3-Confidentiality.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T17:43:16+00:00</t>
+    <t>2025-12-23T08:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-init/ig/CodeSystem-cs-fr-FR-v3-Confidentiality.xlsx
+++ b/nr-init/ig/CodeSystem-cs-fr-FR-v3-Confidentiality.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T08:56:57+00:00</t>
+    <t>2025-12-23T09:21:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
